--- a/MASTER_MANUSCRIPT_LIST_DATA_READINESS_20260504.xlsx
+++ b/MASTER_MANUSCRIPT_LIST_DATA_READINESS_20260504.xlsx
@@ -24,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,6 +41,10 @@
     <font>
       <name val="Arial"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00666666"/>
     </font>
   </fonts>
   <fills count="7">
@@ -102,7 +106,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
@@ -122,6 +126,7 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -487,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1454,7 +1459,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Multimodal Risk: TI-RADS + Bethesda + Final Path</t>
+          <t>Multimodal Risk: TI-RADS + Bethesda + Final Path (per-nodule grain, post-M025)</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1464,7 +1469,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Proposed</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1489,7 +1494,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Same data as #25</t>
+          <t>M025 expansion: re-scope to per-nodule grain framework (use cohort_m025_nodule_level_v1 strict subset n=3,687 + Bethesda bridge from imaging_fna_linkage_v3). Adds joint TI-RADS x Bethesda ROM table at nodule grain; no new data work.</t>
         </is>
       </c>
     </row>
@@ -1499,7 +1504,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Bethesda ROM with NIFTP-Era Stratification</t>
+          <t>Bethesda + TI-RADS ROM with NIFTP/FT-UMP-Era Stratification</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1534,7 +1539,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>NIFTP reclassification logic needed</t>
+          <t>M025 expansion: extend to TI-RADS calibration under NIFTP reclassification (n=58 NIFTP, n=22 FT-UMP in M025 cohort). Single paper instead of two. Needs NIFTP reclass logic vs WHO 2022.</t>
         </is>
       </c>
     </row>
@@ -1580,6 +1585,328 @@
       <c r="I24" s="2" t="inlineStr">
         <is>
           <t>Frozen section canonical rebuilt</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Racial Disparities in TI-RADS Performance (45.5% Black operative cohort)</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>M025 Follow-Up Portfolio</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Proposed</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Priority Active</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>canonical_patient_master (race), cohort_m025_tirads_performance_v1, cohort_m025_nodule_level_v1</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>Same data as M025; pre-specified per-race AUC, per-TR ROM at patient + nodule grain. Target: Thyroid or JAMA Otolaryngology.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Multinodular Attribution Error: Generalizable Framework for RSS Validation (methods)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>M025 Follow-Up Portfolio</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Proposed</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Priority Active</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>NEAR READY</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>imaging_nodule_master_v1 features + reapply EU-TIRADS / K-TIRADS / ATA pattern / AI-TIRADS scoring algorithms</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>Methods extension of M025: re-score same cohort under 4 alternative RSS systems; closed-form attribution-error formula. Target: Stat Med / DPR / J Clin Epi or Thyroid commentary companion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Imaging-Pathology Correlation in Multifocal Thyroid Cancer</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>M025 Follow-Up Portfolio</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Proposed</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Priority Active</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>canonical_path_malignant_events_v1 (4,022 pts; mean 1.61 tumors/pt), canonical_us_nodule_v2</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>Index-nodule concordance (TR-max = path-dominant cancer Y/N); occult cancer rate; size-discordance. Target: Annals of Surgical Oncology, Surgery, or Thyroid.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>TI-RADS Performance in Hashimoto's / CLT Background Thyroid</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>M025 Follow-Up Portfolio</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Proposed</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Priority Active</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>CLT cohort 1,967 pts (per EERC reconciliation), Graves 574 pts; M025 analytic tables</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Per-TR ROM stratified by CLT status; Graves comparator arm; feature-distribution shift analysis. Target: Thyroid or Endocrine Practice.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>LLM + Structured-Feature Pipeline for Retrospective TI-RADS Harmonization (methods)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>M025 Follow-Up Portfolio</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Proposed</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>Priority Active</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>Qwen2.5-32B extraction logs, imaging_nodule_master_v1, us_nodules_tirads_vs_inm_v1_discordance_v1</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>Documents M025 re-scoring pipeline (99.3% structured, 0.7% LLM-aug). Target: Radiology: AI, JAMIA, NPJ Digital Medicine.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>ACR FNA-Eligibility Decision-Curve Analysis (1,553 unnecessary / 472 missed)</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>M025 Follow-Up Portfolio</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Proposed</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>Priority Active</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>M025 analytic tables + size_cm from imaging_nodule_master_v1</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>Net-benefit curves at default ACR thresholds vs alternatives; subgroup decision curves. Target: JACR or Endocrine Practice.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Pre-/Post-2017 Era Comparison: Natural Experiment in TI-RADS Guideline Adoption</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>M025 Follow-Up Portfolio</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Proposed</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>Priority Active</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>NEAR READY</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>M025 era-split tables (pre n=422 / post n=2,953 patients; pre n=381 / post n=3,306 nodules) + canonical_us_exam temporal cols</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>Interrupted-time-series at 2017-05-01 boundary; documentation completeness, FNA yield, malignancy yield. Distinct from #36 (staging-focused). Target: JACR, Radiology, or Thyroid.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>Updated 2026-05-05 — M025 expansions to #45, #46 + new M048-M054 follow-up portfolio appended. See M025_v2_manuscript_DRAFT_v1_0.md for source thesis.</t>
         </is>
       </c>
     </row>

--- a/MASTER_MANUSCRIPT_LIST_DATA_READINESS_20260504.xlsx
+++ b/MASTER_MANUSCRIPT_LIST_DATA_READINESS_20260504.xlsx
@@ -1604,7 +1604,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Proposed</t>
+          <t>Analysis Complete — Awaiting Writing</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">

--- a/MASTER_MANUSCRIPT_LIST_DATA_READINESS_20260504.xlsx
+++ b/MASTER_MANUSCRIPT_LIST_DATA_READINESS_20260504.xlsx
@@ -1604,7 +1604,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Analysis Complete — Awaiting Writing</t>
+          <t>v3 Adjusted Analysis Complete — Awaiting Writing</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">

--- a/MASTER_MANUSCRIPT_LIST_DATA_READINESS_20260504.xlsx
+++ b/MASTER_MANUSCRIPT_LIST_DATA_READINESS_20260504.xlsx
@@ -1604,7 +1604,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>v3 Adjusted Analysis Complete — Awaiting Writing</t>
+          <t>v3.2 Collinearity-Fixed Adjusted Analysis Complete — Awaiting Writing</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1903,6 +1903,7 @@
         </is>
       </c>
     </row>
+    <row r="32"/>
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
         <is>
